--- a/Resultados Utilizados/UMAX_18-10-24_sensibilidade.xlsx
+++ b/Resultados Utilizados/UMAX_18-10-24_sensibilidade.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://etnweb-my.sharepoint.com/personal/saber_eletronuclear_gov_br/Documents/Área de Trabalho/Mestrado/Optimization_HESS/Resultados Utilizados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d5b4fc44e5a41404/Documentos/Mestrado/codigos/optimization_hess/Resultados Utilizados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_7C1513B3D3E0D10AB7792F11595ED87656CDD01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E2FD94A-4193-422A-BF53-78808B469B7E}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_7C1513B3D3E0D10AB7792F11595ED87656CDD01D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2577E4D-FA42-45E8-A80F-E5B1C34C1A94}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -862,28 +862,28 @@
         <v>4</v>
       </c>
       <c r="P6">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S6">
         <v>229.376</v>
       </c>
       <c r="T6">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U6">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V6">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W6">
-        <v>7018234.2753113918</v>
+        <v>7059170.7272634534</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
@@ -933,28 +933,28 @@
         <v>4</v>
       </c>
       <c r="P7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S7">
         <v>229.376</v>
       </c>
       <c r="T7">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U7">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V7">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W7">
-        <v>6859234.2753113927</v>
+        <v>6900170.7272634516</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -1430,28 +1430,28 @@
         <v>4</v>
       </c>
       <c r="P14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q14">
         <v>1</v>
       </c>
       <c r="R14">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S14">
         <v>229.376</v>
       </c>
       <c r="T14">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U14">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V14">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W14">
-        <v>6965234.2753113927</v>
+        <v>7006170.7272634534</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
@@ -1501,28 +1501,28 @@
         <v>4</v>
       </c>
       <c r="P15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q15">
         <v>1</v>
       </c>
       <c r="R15">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S15">
         <v>229.376</v>
       </c>
       <c r="T15">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U15">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V15">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W15">
-        <v>6965234.2753113927</v>
+        <v>7006170.7272634534</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
@@ -1572,28 +1572,28 @@
         <v>4</v>
       </c>
       <c r="P16">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q16">
         <v>1</v>
       </c>
       <c r="R16">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S16">
         <v>229.376</v>
       </c>
       <c r="T16">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U16">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V16">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W16">
-        <v>6965234.2753113927</v>
+        <v>7006170.7272634534</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.25">
@@ -1643,40 +1643,31 @@
         <v>4</v>
       </c>
       <c r="P17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>1258.4960000000001</v>
+        <v>1234.6880000000001</v>
       </c>
       <c r="S17">
         <v>229.376</v>
       </c>
       <c r="T17">
-        <v>1.4976</v>
+        <v>1.3104</v>
       </c>
       <c r="U17">
-        <v>230.87360000000001</v>
+        <v>230.68639999999999</v>
       </c>
       <c r="V17">
-        <v>1425</v>
+        <v>1375</v>
       </c>
       <c r="W17">
-        <v>6965234.2753113927</v>
+        <v>7006170.7272634534</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000  (  X  ) Público    (   ) Interno  (   ) Setorial  (  ) Confidencial  (  ) Dados Pessoais</oddFooter>
-  </headerFooter>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{fb63ac9e-2213-4377-9205-4dbf73e49b6e}" enabled="1" method="Privileged" siteId="{0ad73864-486f-4f58-a5da-a44c51bf5c9b}" removed="0"/>
-</clbl:labelList>
 </file>